--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.4576,0.1054,0.0343,0.5016</t>
-  </si>
-  <si>
-    <t>0.0519,0.0030,0.0027,0.9775</t>
-  </si>
-  <si>
-    <t>0.6542,0.0071,0.0093,0.3675</t>
-  </si>
-  <si>
-    <t>0.0533,0.0260,0.0032,0.9741</t>
-  </si>
-  <si>
-    <t>0.9943,0.0027,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9875,0.0078,0.0023,0.0020</t>
-  </si>
-  <si>
-    <t>0.9883,0.0088,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.9899,0.0042,0.0012,0.0025</t>
-  </si>
-  <si>
-    <t>0.9850,0.0175,0.0013,0.0013</t>
-  </si>
-  <si>
-    <t>0.9820,0.0114,0.0035,0.0029</t>
-  </si>
-  <si>
-    <t>0.9939,0.0050,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0014,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.4537,0.3215,0.2907,0.0838</t>
-  </si>
-  <si>
-    <t>0.3404,0.0244,0.6843,0.0064</t>
-  </si>
-  <si>
-    <t>0.2563,0.0079,0.7976,0.0171</t>
-  </si>
-  <si>
-    <t>0.1677,0.0127,0.8535,0.0154</t>
-  </si>
-  <si>
-    <t>0.7800,0.0521,0.1540,0.0223</t>
-  </si>
-  <si>
-    <t>0.0990,0.8915,0.0294,0.0043</t>
-  </si>
-  <si>
-    <t>0.0522,0.9428,0.0259,0.0005</t>
-  </si>
-  <si>
-    <t>0.5283,0.5536,0.0164,0.0053</t>
-  </si>
-  <si>
-    <t>0.0750,0.9439,0.0065,0.0005</t>
-  </si>
-  <si>
-    <t>0.0206,0.9764,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.5062,0.0241,0.4281,0.0733</t>
-  </si>
-  <si>
-    <t>0.1957,0.0912,0.7035,0.0710</t>
-  </si>
-  <si>
-    <t>0.0331,0.0042,0.9534,0.0161</t>
-  </si>
-  <si>
-    <t>0.2105,0.0053,0.7677,0.0369</t>
-  </si>
-  <si>
-    <t>0.0226,0.0271,0.9548,0.0110</t>
-  </si>
-  <si>
-    <t>0.1051,0.0121,0.9031,0.0076</t>
-  </si>
-  <si>
-    <t>0.0028,0.0032,0.9928,0.0026</t>
-  </si>
-  <si>
-    <t>0.3394,0.6463,0.0559,0.0054</t>
-  </si>
-  <si>
-    <t>0.5221,0.0337,0.4955,0.0353</t>
-  </si>
-  <si>
-    <t>0.0010,0.0031,0.9960,0.0022</t>
-  </si>
-  <si>
-    <t>0.0288,0.8795,0.2691,0.0056</t>
-  </si>
-  <si>
-    <t>0.6528,0.3314,0.0225,0.0273</t>
-  </si>
-  <si>
-    <t>0.6720,0.1473,0.1962,0.0091</t>
-  </si>
-  <si>
-    <t>0.3346,0.5888,0.1029,0.0026</t>
-  </si>
-  <si>
-    <t>0.0198,0.8942,0.5171,0.0026</t>
-  </si>
-  <si>
-    <t>0.0195,0.8350,0.2872,0.0287</t>
-  </si>
-  <si>
-    <t>0.0045,0.0763,0.9651,0.0123</t>
-  </si>
-  <si>
-    <t>0.0089,0.1390,0.9611,0.0025</t>
-  </si>
-  <si>
-    <t>0.0928,0.0081,0.6427,0.2140</t>
-  </si>
-  <si>
-    <t>0.0174,0.0638,0.9636,0.0023</t>
-  </si>
-  <si>
-    <t>0.0020,0.9900,0.0096,0.0017</t>
-  </si>
-  <si>
-    <t>0.0072,0.0039,0.9874,0.0036</t>
-  </si>
-  <si>
-    <t>0.0166,0.8361,0.0272,0.7149</t>
-  </si>
-  <si>
-    <t>0.0020,0.9775,0.0380,0.0545</t>
-  </si>
-  <si>
-    <t>0.0014,0.9901,0.0860,0.0006</t>
-  </si>
-  <si>
-    <t>0.0031,0.9802,0.1664,0.0012</t>
-  </si>
-  <si>
-    <t>0.0012,0.0342,0.9934,0.0014</t>
-  </si>
-  <si>
-    <t>0.0004,0.0308,0.9958,0.0012</t>
-  </si>
-  <si>
-    <t>0.0209,0.0064,0.9333,0.0504</t>
-  </si>
-  <si>
-    <t>0.0265,0.0037,0.9650,0.0127</t>
-  </si>
-  <si>
-    <t>0.0024,0.0048,0.9851,0.0101</t>
-  </si>
-  <si>
-    <t>0.0026,0.0030,0.9933,0.0027</t>
-  </si>
-  <si>
-    <t>0.9712,0.0233,0.0033,0.0029</t>
-  </si>
-  <si>
-    <t>0.8793,0.0750,0.0625,0.0051</t>
-  </si>
-  <si>
-    <t>0.9741,0.0153,0.0019,0.0062</t>
-  </si>
-  <si>
-    <t>0.0034,0.0750,0.9887,0.0015</t>
-  </si>
-  <si>
-    <t>0.9810,0.0133,0.0030,0.0031</t>
-  </si>
-  <si>
-    <t>0.9809,0.0184,0.0036,0.0011</t>
-  </si>
-  <si>
-    <t>0.9681,0.0358,0.0048,0.0012</t>
-  </si>
-  <si>
-    <t>0.0024,0.7694,0.9191,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.0096,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0231,0.1812,0.7694,0.0943</t>
-  </si>
-  <si>
-    <t>0.0005,0.8115,0.9557,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0020,0.9980,0.0005</t>
-  </si>
-  <si>
-    <t>0.0228,0.8499,0.3437,0.0034</t>
-  </si>
-  <si>
-    <t>0.0024,0.9940,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.2613,0.1087,0.7283,0.0088</t>
-  </si>
-  <si>
-    <t>0.6460,0.2277,0.1687,0.0573</t>
-  </si>
-  <si>
-    <t>0.0100,0.0623,0.9797,0.0030</t>
-  </si>
-  <si>
-    <t>0.0006,0.7382,0.9540,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.6039,0.9485,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.9720,0.2089,0.0028</t>
-  </si>
-  <si>
-    <t>0.0010,0.9334,0.7328,0.0010</t>
-  </si>
-  <si>
-    <t>0.0030,0.0014,0.0395,0.9836</t>
-  </si>
-  <si>
-    <t>0.0041,0.0038,0.0012,0.9971</t>
-  </si>
-  <si>
-    <t>0.0142,0.0047,0.0508,0.9613</t>
-  </si>
-  <si>
-    <t>0.0174,0.0461,0.0014,0.9888</t>
-  </si>
-  <si>
-    <t>0.0135,0.0007,0.0032,0.9906</t>
-  </si>
-  <si>
-    <t>0.0027,0.0019,0.0004,0.9983</t>
-  </si>
-  <si>
-    <t>0.0009,0.9641,0.5632,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.4028,0.9778,0.0004</t>
-  </si>
-  <si>
-    <t>0.0349,0.6144,0.6912,0.0095</t>
-  </si>
-  <si>
-    <t>0.0016,0.1682,0.9821,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.8991,0.8282,0.0002</t>
-  </si>
-  <si>
-    <t>0.0029,0.8565,0.7712,0.0010</t>
-  </si>
-  <si>
-    <t>0.9873,0.0048,0.0014,0.0040</t>
-  </si>
-  <si>
-    <t>0.9840,0.0148,0.0027,0.0009</t>
-  </si>
-  <si>
-    <t>0.9843,0.0107,0.0020,0.0022</t>
-  </si>
-  <si>
-    <t>0.9911,0.0055,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9843,0.0141,0.0015,0.0017</t>
-  </si>
-  <si>
-    <t>0.9949,0.0049,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9733,0.0294,0.0025,0.0022</t>
-  </si>
-  <si>
-    <t>0.9553,0.0438,0.0094,0.0024</t>
-  </si>
-  <si>
-    <t>0.9935,0.0021,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9939,0.0070,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9917,0.0038,0.0005,0.0025</t>
-  </si>
-  <si>
-    <t>0.9940,0.0017,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.9949,0.0021,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9899,0.0081,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.9839,0.0061,0.0018,0.0052</t>
-  </si>
-  <si>
-    <t>0.9928,0.0027,0.0006,0.0018</t>
-  </si>
-  <si>
-    <t>0.0011,0.0007,0.9928,0.0083</t>
-  </si>
-  <si>
-    <t>0.1271,0.0472,0.8325,0.0111</t>
-  </si>
-  <si>
-    <t>0.5267,0.0287,0.4070,0.0581</t>
-  </si>
-  <si>
-    <t>0.0448,0.0026,0.9484,0.0103</t>
-  </si>
-  <si>
-    <t>0.1138,0.8910,0.0172,0.0018</t>
-  </si>
-  <si>
-    <t>0.0735,0.9176,0.0279,0.0017</t>
-  </si>
-  <si>
-    <t>0.1131,0.8920,0.0097,0.0032</t>
-  </si>
-  <si>
-    <t>0.1384,0.8753,0.0147,0.0022</t>
-  </si>
-  <si>
-    <t>0.0737,0.8980,0.0673,0.0021</t>
-  </si>
-  <si>
-    <t>0.0242,0.9722,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.4198,0.6014,0.0491,0.0063</t>
-  </si>
-  <si>
-    <t>0.5892,0.1703,0.3180,0.0551</t>
-  </si>
-  <si>
-    <t>0.2668,0.0325,0.7190,0.0568</t>
-  </si>
-  <si>
-    <t>0.5382,0.2123,0.2513,0.1076</t>
-  </si>
-  <si>
-    <t>0.3132,0.4327,0.2855,0.0274</t>
-  </si>
-  <si>
-    <t>0.0688,0.3117,0.0267,0.9251</t>
-  </si>
-  <si>
-    <t>0.0025,0.9912,0.0216,0.0007</t>
-  </si>
-  <si>
-    <t>0.0012,0.9893,0.0228,0.0088</t>
-  </si>
-  <si>
-    <t>0.0360,0.8995,0.0667,0.0414</t>
-  </si>
-  <si>
-    <t>0.0038,0.9780,0.1039,0.0033</t>
-  </si>
-  <si>
-    <t>0.0224,0.9560,0.1382,0.0009</t>
-  </si>
-  <si>
-    <t>0.3612,0.6367,0.0831,0.0046</t>
-  </si>
-  <si>
-    <t>0.1898,0.8002,0.0359,0.0023</t>
-  </si>
-  <si>
-    <t>0.9616,0.0212,0.0113,0.0038</t>
-  </si>
-  <si>
-    <t>0.9688,0.0204,0.0087,0.0027</t>
-  </si>
-  <si>
-    <t>0.9808,0.0065,0.0022,0.0072</t>
-  </si>
-  <si>
-    <t>0.8963,0.0320,0.0644,0.0245</t>
-  </si>
-  <si>
-    <t>0.9836,0.0115,0.0027,0.0019</t>
-  </si>
-  <si>
-    <t>0.9117,0.0806,0.0135,0.0095</t>
-  </si>
-  <si>
-    <t>0.9789,0.0098,0.0036,0.0050</t>
-  </si>
-  <si>
-    <t>0.9821,0.0061,0.0043,0.0040</t>
-  </si>
-  <si>
-    <t>0.0031,0.1771,0.9777,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.2347,0.9945,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.4129,0.9731,0.0005</t>
-  </si>
-  <si>
-    <t>0.0235,0.0183,0.9713,0.0022</t>
-  </si>
-  <si>
-    <t>0.4197,0.0787,0.4612,0.1872</t>
-  </si>
-  <si>
-    <t>0.3966,0.3080,0.3494,0.0665</t>
-  </si>
-  <si>
-    <t>0.4782,0.0210,0.5604,0.0232</t>
-  </si>
-  <si>
-    <t>0.5621,0.0310,0.4177,0.0424</t>
-  </si>
-  <si>
-    <t>0.0129,0.0070,0.0115,0.9867</t>
-  </si>
-  <si>
-    <t>0.0025,0.0010,0.0024,0.9962</t>
-  </si>
-  <si>
-    <t>0.0050,0.0035,0.0055,0.9927</t>
-  </si>
-  <si>
-    <t>0.0078,0.0047,0.0013,0.9950</t>
-  </si>
-  <si>
-    <t>0.0023,0.8768,0.7522,0.0025</t>
-  </si>
-  <si>
-    <t>0.9922,0.0040,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.4248,0.5718,0.0490,0.0050</t>
-  </si>
-  <si>
-    <t>0.9576,0.0187,0.0131,0.0067</t>
-  </si>
-  <si>
-    <t>0.9427,0.0847,0.0035,0.0014</t>
-  </si>
-  <si>
-    <t>0.9656,0.0079,0.0119,0.0055</t>
-  </si>
-  <si>
-    <t>0.3486,0.1393,0.0057,0.6652</t>
-  </si>
-  <si>
-    <t>0.9746,0.0063,0.0014,0.0145</t>
-  </si>
-  <si>
-    <t>0.0013,0.0346,0.9888,0.0086</t>
-  </si>
-  <si>
-    <t>0.9502,0.0035,0.0055,0.0281</t>
-  </si>
-  <si>
-    <t>0.8857,0.0081,0.0295,0.0513</t>
-  </si>
-  <si>
-    <t>0.3615,0.5324,0.1999,0.0224</t>
-  </si>
-  <si>
-    <t>0.8493,0.0726,0.0443,0.0260</t>
-  </si>
-  <si>
-    <t>0.5842,0.3935,0.0912,0.0129</t>
-  </si>
-  <si>
-    <t>0.4090,0.5432,0.0356,0.0585</t>
-  </si>
-  <si>
-    <t>0.6893,0.0724,0.2554,0.0208</t>
-  </si>
-  <si>
-    <t>0.4965,0.5036,0.1010,0.0201</t>
-  </si>
-  <si>
-    <t>0.9908,0.0041,0.0013,0.0020</t>
-  </si>
-  <si>
-    <t>0.9804,0.0063,0.0018,0.0079</t>
-  </si>
-  <si>
-    <t>0.9805,0.0067,0.0033,0.0071</t>
-  </si>
-  <si>
-    <t>0.9886,0.0044,0.0009,0.0031</t>
-  </si>
-  <si>
-    <t>0.9882,0.0039,0.0021,0.0022</t>
-  </si>
-  <si>
-    <t>0.9795,0.0034,0.0017,0.0104</t>
-  </si>
-  <si>
-    <t>0.9853,0.0117,0.0016,0.0018</t>
-  </si>
-  <si>
-    <t>0.9764,0.0099,0.0047,0.0066</t>
-  </si>
-  <si>
-    <t>0.5220,0.5918,0.0171,0.0038</t>
-  </si>
-  <si>
-    <t>0.7248,0.4174,0.0068,0.0010</t>
-  </si>
-  <si>
-    <t>0.7075,0.4206,0.0121,0.0010</t>
-  </si>
-  <si>
-    <t>0.5954,0.2503,0.2800,0.0303</t>
-  </si>
-  <si>
-    <t>0.9044,0.1222,0.0108,0.0022</t>
-  </si>
-  <si>
-    <t>0.9467,0.0318,0.0071,0.0129</t>
-  </si>
-  <si>
-    <t>0.9559,0.0478,0.0064,0.0008</t>
-  </si>
-  <si>
-    <t>0.4231,0.6410,0.0178,0.0044</t>
-  </si>
-  <si>
-    <t>0.0013,0.0115,0.9970,0.0004</t>
-  </si>
-  <si>
-    <t>0.9658,0.0288,0.0073,0.0017</t>
-  </si>
-  <si>
-    <t>0.0052,0.0159,0.9860,0.0029</t>
-  </si>
-  <si>
-    <t>0.0012,0.0196,0.9912,0.0038</t>
-  </si>
-  <si>
-    <t>0.2521,0.0118,0.7985,0.0171</t>
-  </si>
-  <si>
-    <t>0.0028,0.0229,0.9839,0.0078</t>
-  </si>
-  <si>
-    <t>0.0038,0.0025,0.9938,0.0012</t>
-  </si>
-  <si>
-    <t>0.0052,0.0007,0.9941,0.0010</t>
-  </si>
-  <si>
-    <t>0.0014,0.0041,0.9951,0.0016</t>
-  </si>
-  <si>
-    <t>0.5303,0.0304,0.4873,0.0219</t>
-  </si>
-  <si>
-    <t>0.5443,0.0045,0.6078,0.0059</t>
-  </si>
-  <si>
-    <t>0.1972,0.0101,0.8238,0.0257</t>
-  </si>
-  <si>
-    <t>0.2214,0.0352,0.7794,0.0041</t>
-  </si>
-  <si>
-    <t>0.2278,0.6272,0.2566,0.0131</t>
-  </si>
-  <si>
-    <t>0.2591,0.6401,0.1141,0.0097</t>
-  </si>
-  <si>
-    <t>0.3629,0.0489,0.6311,0.0386</t>
-  </si>
-  <si>
-    <t>0.6424,0.0832,0.2730,0.0331</t>
-  </si>
-  <si>
-    <t>0.4857,0.4464,0.0793,0.0008</t>
-  </si>
-  <si>
-    <t>0.5366,0.5403,0.0277,0.0016</t>
-  </si>
-  <si>
-    <t>0.6656,0.4280,0.0180,0.0068</t>
-  </si>
-  <si>
-    <t>0.9762,0.0150,0.0048,0.0046</t>
-  </si>
-  <si>
-    <t>0.6181,0.4705,0.0176,0.0019</t>
-  </si>
-  <si>
-    <t>0.5771,0.0915,0.3756,0.0315</t>
-  </si>
-  <si>
-    <t>0.6581,0.0656,0.2704,0.0305</t>
-  </si>
-  <si>
-    <t>0.3794,0.0149,0.4667,0.1222</t>
-  </si>
-  <si>
-    <t>0.3730,0.0043,0.7621,0.0048</t>
-  </si>
-  <si>
-    <t>0.3407,0.0073,0.6536,0.0456</t>
-  </si>
-  <si>
-    <t>0.0484,0.0189,0.9063,0.0504</t>
-  </si>
-  <si>
-    <t>0.0022,0.1289,0.9769,0.0025</t>
-  </si>
-  <si>
-    <t>0.0125,0.1757,0.9414,0.0080</t>
-  </si>
-  <si>
-    <t>0.0206,0.0475,0.9399,0.0239</t>
-  </si>
-  <si>
-    <t>0.0169,0.0528,0.9479,0.0113</t>
-  </si>
-  <si>
-    <t>0.9893,0.0041,0.0009,0.0035</t>
-  </si>
-  <si>
-    <t>0.9896,0.0052,0.0009,0.0029</t>
-  </si>
-  <si>
-    <t>0.9832,0.0176,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.9879,0.0046,0.0034,0.0023</t>
-  </si>
-  <si>
-    <t>0.9908,0.0057,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9908,0.0062,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9892,0.0044,0.0011,0.0024</t>
-  </si>
-  <si>
-    <t>0.9871,0.0071,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.3637,0.0087,0.7542,0.0085</t>
-  </si>
-  <si>
-    <t>0.5500,0.2391,0.3068,0.0274</t>
-  </si>
-  <si>
-    <t>0.8847,0.0180,0.0142,0.0703</t>
-  </si>
-  <si>
-    <t>0.0026,0.0008,0.9966,0.0006</t>
-  </si>
-  <si>
-    <t>0.0020,0.0088,0.9916,0.0037</t>
-  </si>
-  <si>
-    <t>0.0680,0.0256,0.9246,0.0048</t>
-  </si>
-  <si>
-    <t>0.0007,0.0018,0.9938,0.0064</t>
-  </si>
-  <si>
-    <t>0.1213,0.0062,0.9086,0.0040</t>
-  </si>
-  <si>
-    <t>0.0006,0.0805,0.9957,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0057,0.9944,0.0036</t>
-  </si>
-  <si>
-    <t>0.0230,0.0196,0.9646,0.0049</t>
-  </si>
-  <si>
-    <t>0.7006,0.0461,0.2488,0.0165</t>
-  </si>
-  <si>
-    <t>0.6617,0.0080,0.1600,0.0712</t>
-  </si>
-  <si>
-    <t>0.2257,0.0226,0.1315,0.6885</t>
-  </si>
-  <si>
-    <t>0.9840,0.0092,0.0016,0.0028</t>
-  </si>
-  <si>
-    <t>0.9919,0.0061,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9947,0.0035,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9726,0.0239,0.0070,0.0013</t>
-  </si>
-  <si>
-    <t>0.9755,0.0102,0.0027,0.0090</t>
-  </si>
-  <si>
-    <t>0.9916,0.0078,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9842,0.0135,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.9763,0.0126,0.0064,0.0029</t>
-  </si>
-  <si>
-    <t>0.0866,0.0155,0.9112,0.0084</t>
-  </si>
-  <si>
-    <t>0.0026,0.0081,0.9934,0.0013</t>
-  </si>
-  <si>
-    <t>0.0031,0.0170,0.9911,0.0013</t>
-  </si>
-  <si>
-    <t>0.2625,0.0729,0.6808,0.0309</t>
-  </si>
-  <si>
-    <t>0.0018,0.0035,0.9958,0.0009</t>
-  </si>
-  <si>
-    <t>0.1229,0.0286,0.3486,0.6013</t>
-  </si>
-  <si>
-    <t>0.2106,0.0079,0.8096,0.0203</t>
-  </si>
-  <si>
-    <t>0.0464,0.0154,0.9489,0.0086</t>
-  </si>
-  <si>
-    <t>0.6729,0.0256,0.0577,0.2804</t>
-  </si>
-  <si>
-    <t>0.0279,0.0357,0.0325,0.9674</t>
-  </si>
-  <si>
-    <t>0.0378,0.0100,0.0034,0.9793</t>
-  </si>
-  <si>
-    <t>0.0152,0.0003,0.0003,0.9928</t>
-  </si>
-  <si>
-    <t>0.0033,0.0002,0.0004,0.9980</t>
-  </si>
-  <si>
-    <t>0.5777,0.0252,0.0354,0.3965</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.5224,0.1553,0.0440,0.3326</t>
+  </si>
+  <si>
+    <t>0.0978,0.0010,0.0024,0.9612</t>
+  </si>
+  <si>
+    <t>0.7591,0.0159,0.0480,0.1219</t>
+  </si>
+  <si>
+    <t>0.1020,0.0030,0.0014,0.9609</t>
+  </si>
+  <si>
+    <t>0.9807,0.0155,0.0034,0.0018</t>
+  </si>
+  <si>
+    <t>0.9936,0.0038,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9881,0.0066,0.0022,0.0017</t>
+  </si>
+  <si>
+    <t>0.9941,0.0049,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9889,0.0048,0.0008,0.0026</t>
+  </si>
+  <si>
+    <t>0.9899,0.0085,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0016,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9957,0.0017,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.6840,0.0139,0.2848,0.0226</t>
+  </si>
+  <si>
+    <t>0.4338,0.0522,0.5493,0.0369</t>
+  </si>
+  <si>
+    <t>0.3936,0.0121,0.6913,0.0083</t>
+  </si>
+  <si>
+    <t>0.1317,0.0283,0.8529,0.0091</t>
+  </si>
+  <si>
+    <t>0.7185,0.0764,0.2063,0.0155</t>
+  </si>
+  <si>
+    <t>0.0461,0.9532,0.0069,0.0011</t>
+  </si>
+  <si>
+    <t>0.1024,0.9051,0.0273,0.0014</t>
+  </si>
+  <si>
+    <t>0.7368,0.3242,0.0233,0.0038</t>
+  </si>
+  <si>
+    <t>0.0544,0.9526,0.0034,0.0008</t>
+  </si>
+  <si>
+    <t>0.0085,0.9873,0.0086,0.0001</t>
+  </si>
+  <si>
+    <t>0.4745,0.0346,0.4898,0.0454</t>
+  </si>
+  <si>
+    <t>0.0715,0.0038,0.9014,0.0283</t>
+  </si>
+  <si>
+    <t>0.0143,0.0052,0.9817,0.0028</t>
+  </si>
+  <si>
+    <t>0.0178,0.0119,0.9208,0.0755</t>
+  </si>
+  <si>
+    <t>0.0264,0.0025,0.9781,0.0030</t>
+  </si>
+  <si>
+    <t>0.0904,0.0071,0.9118,0.0160</t>
+  </si>
+  <si>
+    <t>0.0054,0.0024,0.9894,0.0050</t>
+  </si>
+  <si>
+    <t>0.2849,0.6998,0.0633,0.0032</t>
+  </si>
+  <si>
+    <t>0.2225,0.3952,0.4085,0.0193</t>
+  </si>
+  <si>
+    <t>0.0001,0.0028,0.9985,0.0008</t>
+  </si>
+  <si>
+    <t>0.0362,0.8900,0.1048,0.0066</t>
+  </si>
+  <si>
+    <t>0.8734,0.0293,0.0795,0.0218</t>
+  </si>
+  <si>
+    <t>0.5350,0.2031,0.2697,0.0237</t>
+  </si>
+  <si>
+    <t>0.5915,0.5035,0.0206,0.0010</t>
+  </si>
+  <si>
+    <t>0.0368,0.8495,0.4686,0.0044</t>
+  </si>
+  <si>
+    <t>0.0275,0.5899,0.7296,0.0118</t>
+  </si>
+  <si>
+    <t>0.0166,0.0208,0.9737,0.0056</t>
+  </si>
+  <si>
+    <t>0.0486,0.0419,0.9165,0.0188</t>
+  </si>
+  <si>
+    <t>0.1085,0.0410,0.5404,0.3564</t>
+  </si>
+  <si>
+    <t>0.0263,0.4303,0.7947,0.0146</t>
+  </si>
+  <si>
+    <t>0.0059,0.9763,0.0385,0.0010</t>
+  </si>
+  <si>
+    <t>0.0108,0.0372,0.9542,0.0275</t>
+  </si>
+  <si>
+    <t>0.0151,0.8327,0.0204,0.7931</t>
+  </si>
+  <si>
+    <t>0.0014,0.9916,0.0363,0.0017</t>
+  </si>
+  <si>
+    <t>0.0048,0.9763,0.0856,0.0023</t>
+  </si>
+  <si>
+    <t>0.0018,0.9831,0.0312,0.0200</t>
+  </si>
+  <si>
+    <t>0.0092,0.1664,0.9618,0.0047</t>
+  </si>
+  <si>
+    <t>0.0051,0.2075,0.9719,0.0022</t>
+  </si>
+  <si>
+    <t>0.0437,0.0203,0.9064,0.0474</t>
+  </si>
+  <si>
+    <t>0.0050,0.0027,0.9901,0.0033</t>
+  </si>
+  <si>
+    <t>0.0207,0.0070,0.9531,0.0268</t>
+  </si>
+  <si>
+    <t>0.0011,0.0088,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.9699,0.0311,0.0052,0.0012</t>
+  </si>
+  <si>
+    <t>0.9820,0.0053,0.0019,0.0072</t>
+  </si>
+  <si>
+    <t>0.8861,0.0582,0.0684,0.0236</t>
+  </si>
+  <si>
+    <t>0.0090,0.1047,0.9750,0.0044</t>
+  </si>
+  <si>
+    <t>0.9563,0.0284,0.0176,0.0051</t>
+  </si>
+  <si>
+    <t>0.9919,0.0052,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9772,0.0163,0.0035,0.0031</t>
+  </si>
+  <si>
+    <t>0.0010,0.8008,0.9246,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0036,0.9983,0.0009</t>
+  </si>
+  <si>
+    <t>0.0059,0.0166,0.9844,0.0034</t>
+  </si>
+  <si>
+    <t>0.0014,0.6035,0.9630,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0031,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.0846,0.9030,0.0317,0.0036</t>
+  </si>
+  <si>
+    <t>0.0051,0.9901,0.0034,0.0003</t>
+  </si>
+  <si>
+    <t>0.3270,0.0356,0.7514,0.0084</t>
+  </si>
+  <si>
+    <t>0.4529,0.1824,0.4480,0.0180</t>
+  </si>
+  <si>
+    <t>0.0030,0.0548,0.9837,0.0031</t>
+  </si>
+  <si>
+    <t>0.0007,0.7188,0.9549,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.8572,0.8545,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.9892,0.1138,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9653,0.4730,0.0015</t>
+  </si>
+  <si>
+    <t>0.0490,0.0013,0.0053,0.9676</t>
+  </si>
+  <si>
+    <t>0.0098,0.0040,0.0016,0.9934</t>
+  </si>
+  <si>
+    <t>0.0346,0.0097,0.0032,0.9783</t>
+  </si>
+  <si>
+    <t>0.0068,0.0073,0.0018,0.9951</t>
+  </si>
+  <si>
+    <t>0.0032,0.0039,0.0032,0.9965</t>
+  </si>
+  <si>
+    <t>0.0180,0.0037,0.0014,0.9910</t>
+  </si>
+  <si>
+    <t>0.0002,0.9786,0.7088,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.5927,0.9706,0.0004</t>
+  </si>
+  <si>
+    <t>0.0345,0.5001,0.7634,0.0169</t>
+  </si>
+  <si>
+    <t>0.0076,0.0246,0.9847,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.9269,0.8065,0.0001</t>
+  </si>
+  <si>
+    <t>0.0069,0.7704,0.8036,0.0018</t>
+  </si>
+  <si>
+    <t>0.9913,0.0048,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9744,0.0137,0.0032,0.0061</t>
+  </si>
+  <si>
+    <t>0.9757,0.0232,0.0033,0.0020</t>
+  </si>
+  <si>
+    <t>0.9842,0.0140,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9848,0.0085,0.0023,0.0024</t>
+  </si>
+  <si>
+    <t>0.9942,0.0031,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9828,0.0170,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9833,0.0166,0.0027,0.0011</t>
+  </si>
+  <si>
+    <t>0.9945,0.0030,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9939,0.0044,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9922,0.0032,0.0006,0.0022</t>
+  </si>
+  <si>
+    <t>0.9898,0.0036,0.0010,0.0023</t>
+  </si>
+  <si>
+    <t>0.9874,0.0055,0.0016,0.0024</t>
+  </si>
+  <si>
+    <t>0.9933,0.0034,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9916,0.0036,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9942,0.0020,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9971,0.0059</t>
+  </si>
+  <si>
+    <t>0.0384,0.0213,0.9617,0.0014</t>
+  </si>
+  <si>
+    <t>0.5488,0.0462,0.3188,0.0950</t>
+  </si>
+  <si>
+    <t>0.0114,0.0047,0.9889,0.0006</t>
+  </si>
+  <si>
+    <t>0.1046,0.9018,0.0083,0.0018</t>
+  </si>
+  <si>
+    <t>0.0624,0.9092,0.0626,0.0027</t>
+  </si>
+  <si>
+    <t>0.0840,0.9126,0.0123,0.0027</t>
+  </si>
+  <si>
+    <t>0.3046,0.7467,0.0128,0.0030</t>
+  </si>
+  <si>
+    <t>0.1972,0.7811,0.0565,0.0013</t>
+  </si>
+  <si>
+    <t>0.0365,0.9662,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.6091,0.4056,0.0354,0.0026</t>
+  </si>
+  <si>
+    <t>0.5554,0.3292,0.1720,0.0251</t>
+  </si>
+  <si>
+    <t>0.4617,0.0160,0.5619,0.0320</t>
+  </si>
+  <si>
+    <t>0.2731,0.5163,0.1631,0.2446</t>
+  </si>
+  <si>
+    <t>0.1965,0.2615,0.2436,0.5193</t>
+  </si>
+  <si>
+    <t>0.3674,0.0252,0.2640,0.3721</t>
+  </si>
+  <si>
+    <t>0.0029,0.9817,0.0414,0.0118</t>
+  </si>
+  <si>
+    <t>0.0004,0.9941,0.0058,0.0160</t>
+  </si>
+  <si>
+    <t>0.0920,0.8304,0.1046,0.0670</t>
+  </si>
+  <si>
+    <t>0.0017,0.9290,0.7773,0.0018</t>
+  </si>
+  <si>
+    <t>0.0249,0.9550,0.1238,0.0006</t>
+  </si>
+  <si>
+    <t>0.3001,0.5759,0.2358,0.0073</t>
+  </si>
+  <si>
+    <t>0.5758,0.4288,0.0645,0.0030</t>
+  </si>
+  <si>
+    <t>0.9336,0.0274,0.0165,0.0289</t>
+  </si>
+  <si>
+    <t>0.9645,0.0230,0.0080,0.0059</t>
+  </si>
+  <si>
+    <t>0.9859,0.0019,0.0005,0.0107</t>
+  </si>
+  <si>
+    <t>0.9625,0.0188,0.0091,0.0094</t>
+  </si>
+  <si>
+    <t>0.9837,0.0094,0.0015,0.0034</t>
+  </si>
+  <si>
+    <t>0.8757,0.0835,0.0470,0.0147</t>
+  </si>
+  <si>
+    <t>0.9874,0.0045,0.0006,0.0038</t>
+  </si>
+  <si>
+    <t>0.9682,0.0034,0.0022,0.0221</t>
+  </si>
+  <si>
+    <t>0.0006,0.5349,0.9746,0.0001</t>
+  </si>
+  <si>
+    <t>0.0087,0.3847,0.9181,0.0016</t>
+  </si>
+  <si>
+    <t>0.0139,0.0911,0.9562,0.0064</t>
+  </si>
+  <si>
+    <t>0.0191,0.0421,0.9608,0.0047</t>
+  </si>
+  <si>
+    <t>0.5836,0.1658,0.3007,0.0441</t>
+  </si>
+  <si>
+    <t>0.5773,0.0904,0.3676,0.0261</t>
+  </si>
+  <si>
+    <t>0.3499,0.0061,0.7726,0.0083</t>
+  </si>
+  <si>
+    <t>0.6215,0.1486,0.2591,0.0107</t>
+  </si>
+  <si>
+    <t>0.0533,0.0031,0.0174,0.9497</t>
+  </si>
+  <si>
+    <t>0.0033,0.0015,0.0070,0.9936</t>
+  </si>
+  <si>
+    <t>0.0076,0.0141,0.0032,0.9936</t>
+  </si>
+  <si>
+    <t>0.0131,0.0024,0.0067,0.9888</t>
+  </si>
+  <si>
+    <t>0.0041,0.5862,0.8556,0.0079</t>
+  </si>
+  <si>
+    <t>0.9727,0.0194,0.0049,0.0032</t>
+  </si>
+  <si>
+    <t>0.5359,0.5343,0.0136,0.0096</t>
+  </si>
+  <si>
+    <t>0.9573,0.0077,0.0060,0.0261</t>
+  </si>
+  <si>
+    <t>0.9339,0.0560,0.0180,0.0039</t>
+  </si>
+  <si>
+    <t>0.8936,0.0652,0.0343,0.0187</t>
+  </si>
+  <si>
+    <t>0.1794,0.0423,0.0281,0.8710</t>
+  </si>
+  <si>
+    <t>0.9820,0.0030,0.0008,0.0094</t>
+  </si>
+  <si>
+    <t>0.0010,0.0207,0.9874,0.0137</t>
+  </si>
+  <si>
+    <t>0.8352,0.0025,0.0310,0.0768</t>
+  </si>
+  <si>
+    <t>0.9585,0.0088,0.0111,0.0096</t>
+  </si>
+  <si>
+    <t>0.7532,0.2275,0.0390,0.0174</t>
+  </si>
+  <si>
+    <t>0.7373,0.1476,0.1369,0.0090</t>
+  </si>
+  <si>
+    <t>0.6624,0.1675,0.2164,0.0128</t>
+  </si>
+  <si>
+    <t>0.4651,0.2977,0.3018,0.0254</t>
+  </si>
+  <si>
+    <t>0.6536,0.0982,0.2990,0.0144</t>
+  </si>
+  <si>
+    <t>0.6100,0.1117,0.3338,0.0194</t>
+  </si>
+  <si>
+    <t>0.9827,0.0062,0.0013,0.0070</t>
+  </si>
+  <si>
+    <t>0.9861,0.0070,0.0022,0.0030</t>
+  </si>
+  <si>
+    <t>0.9828,0.0089,0.0041,0.0028</t>
+  </si>
+  <si>
+    <t>0.9687,0.0070,0.0058,0.0120</t>
+  </si>
+  <si>
+    <t>0.9824,0.0132,0.0022,0.0021</t>
+  </si>
+  <si>
+    <t>0.9813,0.0073,0.0032,0.0063</t>
+  </si>
+  <si>
+    <t>0.9898,0.0021,0.0007,0.0042</t>
+  </si>
+  <si>
+    <t>0.9898,0.0039,0.0009,0.0028</t>
+  </si>
+  <si>
+    <t>0.7590,0.2872,0.0329,0.0071</t>
+  </si>
+  <si>
+    <t>0.8444,0.1868,0.0186,0.0042</t>
+  </si>
+  <si>
+    <t>0.5297,0.4942,0.0552,0.0091</t>
+  </si>
+  <si>
+    <t>0.8412,0.0872,0.0910,0.0304</t>
+  </si>
+  <si>
+    <t>0.9587,0.0387,0.0064,0.0043</t>
+  </si>
+  <si>
+    <t>0.9559,0.0339,0.0077,0.0035</t>
+  </si>
+  <si>
+    <t>0.9297,0.0832,0.0120,0.0022</t>
+  </si>
+  <si>
+    <t>0.8911,0.0922,0.0327,0.0030</t>
+  </si>
+  <si>
+    <t>0.0020,0.0259,0.9948,0.0004</t>
+  </si>
+  <si>
+    <t>0.8731,0.1103,0.0332,0.0019</t>
+  </si>
+  <si>
+    <t>0.0056,0.0022,0.9891,0.0037</t>
+  </si>
+  <si>
+    <t>0.0016,0.2806,0.9833,0.0009</t>
+  </si>
+  <si>
+    <t>0.0254,0.0032,0.9829,0.0008</t>
+  </si>
+  <si>
+    <t>0.0013,0.0100,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.0025,0.9919,0.0021</t>
+  </si>
+  <si>
+    <t>0.0324,0.0093,0.9667,0.0049</t>
+  </si>
+  <si>
+    <t>0.0028,0.0054,0.9954,0.0005</t>
+  </si>
+  <si>
+    <t>0.4318,0.0138,0.6293,0.0174</t>
+  </si>
+  <si>
+    <t>0.1967,0.0041,0.8725,0.0039</t>
+  </si>
+  <si>
+    <t>0.6469,0.0474,0.3481,0.0228</t>
+  </si>
+  <si>
+    <t>0.3943,0.2783,0.3540,0.0138</t>
+  </si>
+  <si>
+    <t>0.1511,0.1653,0.7038,0.0046</t>
+  </si>
+  <si>
+    <t>0.5324,0.0088,0.6038,0.0072</t>
+  </si>
+  <si>
+    <t>0.0848,0.0166,0.9092,0.0146</t>
+  </si>
+  <si>
+    <t>0.4305,0.1209,0.4619,0.0157</t>
+  </si>
+  <si>
+    <t>0.8866,0.1307,0.0146,0.0021</t>
+  </si>
+  <si>
+    <t>0.4367,0.6116,0.0482,0.0041</t>
+  </si>
+  <si>
+    <t>0.9291,0.0876,0.0091,0.0014</t>
+  </si>
+  <si>
+    <t>0.9791,0.0166,0.0035,0.0019</t>
+  </si>
+  <si>
+    <t>0.9281,0.0540,0.0262,0.0052</t>
+  </si>
+  <si>
+    <t>0.4714,0.2719,0.2926,0.0231</t>
+  </si>
+  <si>
+    <t>0.7033,0.0479,0.2576,0.0162</t>
+  </si>
+  <si>
+    <t>0.6583,0.0093,0.2352,0.0431</t>
+  </si>
+  <si>
+    <t>0.5497,0.0138,0.4725,0.0224</t>
+  </si>
+  <si>
+    <t>0.7589,0.0199,0.1995,0.0233</t>
+  </si>
+  <si>
+    <t>0.1682,0.0168,0.7642,0.0943</t>
+  </si>
+  <si>
+    <t>0.0739,0.1219,0.8684,0.0225</t>
+  </si>
+  <si>
+    <t>0.0290,0.1109,0.9124,0.0163</t>
+  </si>
+  <si>
+    <t>0.0470,0.0215,0.9533,0.0033</t>
+  </si>
+  <si>
+    <t>0.0073,0.3480,0.9212,0.0017</t>
+  </si>
+  <si>
+    <t>0.9873,0.0025,0.0003,0.0073</t>
+  </si>
+  <si>
+    <t>0.9639,0.0324,0.0030,0.0058</t>
+  </si>
+  <si>
+    <t>0.9880,0.0072,0.0017,0.0021</t>
+  </si>
+  <si>
+    <t>0.9787,0.0139,0.0048,0.0030</t>
+  </si>
+  <si>
+    <t>0.9799,0.0167,0.0025,0.0022</t>
+  </si>
+  <si>
+    <t>0.9853,0.0080,0.0026,0.0031</t>
+  </si>
+  <si>
+    <t>0.9865,0.0055,0.0021,0.0031</t>
+  </si>
+  <si>
+    <t>0.9917,0.0045,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.1823,0.0094,0.7990,0.0425</t>
+  </si>
+  <si>
+    <t>0.2107,0.3315,0.5913,0.0241</t>
+  </si>
+  <si>
+    <t>0.8249,0.0213,0.0767,0.0750</t>
+  </si>
+  <si>
+    <t>0.0024,0.0161,0.9924,0.0012</t>
+  </si>
+  <si>
+    <t>0.0008,0.0113,0.9954,0.0019</t>
+  </si>
+  <si>
+    <t>0.0154,0.0057,0.9842,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9988,0.0009</t>
+  </si>
+  <si>
+    <t>0.0253,0.0022,0.9764,0.0037</t>
+  </si>
+  <si>
+    <t>0.0016,0.0044,0.9967,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0013,0.9984,0.0004</t>
+  </si>
+  <si>
+    <t>0.5360,0.0108,0.5508,0.0113</t>
+  </si>
+  <si>
+    <t>0.4183,0.0036,0.6709,0.0133</t>
+  </si>
+  <si>
+    <t>0.5308,0.0595,0.1940,0.2784</t>
+  </si>
+  <si>
+    <t>0.6595,0.0159,0.3333,0.0296</t>
+  </si>
+  <si>
+    <t>0.9713,0.0257,0.0060,0.0021</t>
+  </si>
+  <si>
+    <t>0.9823,0.0144,0.0037,0.0018</t>
+  </si>
+  <si>
+    <t>0.9932,0.0034,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9864,0.0151,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9894,0.0030,0.0006,0.0037</t>
+  </si>
+  <si>
+    <t>0.9665,0.0265,0.0091,0.0026</t>
+  </si>
+  <si>
+    <t>0.9805,0.0172,0.0023,0.0021</t>
+  </si>
+  <si>
+    <t>0.9158,0.0840,0.0108,0.0118</t>
+  </si>
+  <si>
+    <t>0.0689,0.1613,0.8066,0.0060</t>
+  </si>
+  <si>
+    <t>0.0004,0.0397,0.9946,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0028,0.9975,0.0006</t>
+  </si>
+  <si>
+    <t>0.0362,0.0825,0.8418,0.0807</t>
+  </si>
+  <si>
+    <t>0.0024,0.0040,0.9849,0.0155</t>
+  </si>
+  <si>
+    <t>0.2932,0.1186,0.1505,0.6015</t>
+  </si>
+  <si>
+    <t>0.3277,0.0061,0.5975,0.0542</t>
+  </si>
+  <si>
+    <t>0.0108,0.0792,0.9265,0.0514</t>
+  </si>
+  <si>
+    <t>0.6252,0.0021,0.0058,0.4507</t>
+  </si>
+  <si>
+    <t>0.0458,0.0343,0.0509,0.9499</t>
+  </si>
+  <si>
+    <t>0.0832,0.0024,0.0011,0.9651</t>
+  </si>
+  <si>
+    <t>0.0057,0.0006,0.0010,0.9956</t>
+  </si>
+  <si>
+    <t>0.0027,0.0006,0.0006,0.9979</t>
+  </si>
+  <si>
+    <t>0.1778,0.0257,0.0204,0.8843</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,10 +2469,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +3001,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3113,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,10 +4233,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,10 +4457,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,10 +5213,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
